--- a/data/orders-2026-05.xlsx
+++ b/data/orders-2026-05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
   <si>
     <t>createdAt</t>
   </si>
@@ -64,36 +64,42 @@
     <t>2026-05-03T16:09:23.606Z</t>
   </si>
   <si>
+    <t>2026-06-08T09:02:19.861Z</t>
+  </si>
+  <si>
+    <t>JMN374371359</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>457146567376371712</t>
+  </si>
+  <si>
+    <t>jeff897564231</t>
+  </si>
+  <si>
+    <t>絕密2h</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>24410241344437</t>
+  </si>
+  <si>
+    <t>1202920341123375114</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>JMN374371359</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>457146567376371712</t>
-  </si>
-  <si>
-    <t>jeff897564231</t>
-  </si>
-  <si>
-    <t>絕密2h</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>24410241344437</t>
-  </si>
-  <si>
-    <t>1202920341123375114</t>
-  </si>
-  <si>
     <t>2026-05-16T12:05:13.066Z</t>
   </si>
   <si>
+    <t>2026-06-08T09:02:27.355Z</t>
+  </si>
+  <si>
     <t>EYR153014733</t>
   </si>
   <si>
@@ -127,6 +133,9 @@
     <t>2026-05-26T11:44:23.898Z</t>
   </si>
   <si>
+    <t>2026-06-08T09:02:35.697Z</t>
+  </si>
+  <si>
     <t>WNZ050786718</t>
   </si>
   <si>
@@ -142,6 +151,9 @@
     <t>2026-05-29T16:27:05.802Z</t>
   </si>
   <si>
+    <t>2026-06-08T09:02:01.035Z</t>
+  </si>
+  <si>
     <t>MWH480213718</t>
   </si>
   <si>
@@ -161,6 +173,9 @@
   </si>
   <si>
     <t>2026-05-31T10:39:14.474Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:02:52.599Z</t>
   </si>
   <si>
     <t>QBA125733400</t>
@@ -650,42 +665,42 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>220</v>
@@ -700,42 +715,42 @@
         <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>1231</v>
@@ -750,42 +765,42 @@
         <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5">
         <v>1100</v>
@@ -800,119 +815,119 @@
         <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>1800</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H7">
         <v>200</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
